--- a/AAII_Financials/Yearly/AGNC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AGNC_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>AGNC</t>
   </si>
@@ -656,203 +656,215 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="3">
+        <v>2538000</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3">
         <v>912000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>501000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2920000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1360000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1365000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1122000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>684000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>280000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1976000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1952000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1135200</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2287000</v>
+      </c>
+      <c r="E9" s="3">
         <v>625000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>75000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>674000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2149000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1173000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>524000</v>
-      </c>
-      <c r="J9" s="3">
-        <v>446000</v>
       </c>
       <c r="K9" s="3">
         <v>446000</v>
       </c>
       <c r="L9" s="3">
+        <v>446000</v>
+      </c>
+      <c r="M9" s="3">
         <v>491000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>672000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>625000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>339400</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="D10" s="3">
+        <v>251000</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="3">
         <v>837000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-173000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>771000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>187000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>841000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>676000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>238000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-211000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1304000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1327000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>795800</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -869,8 +881,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -910,9 +923,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -952,9 +968,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -970,12 +989,12 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>-42000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
@@ -985,8 +1004,8 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -994,9 +1013,12 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1036,9 +1058,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1052,92 +1077,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2383000</v>
+      </c>
+      <c r="E17" s="3">
         <v>699000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>163000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>767000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2232000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1231000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>594000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>499000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>469000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>513000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>704000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>656000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>358500</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="D18" s="3">
+        <v>155000</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3">
         <v>749000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-266000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>688000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>129000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>771000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>623000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>215000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-233000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1272000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1296000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>776700</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1154,16 +1186,17 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1195,9 +1228,12 @@
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1207,24 +1243,24 @@
       <c r="E21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3">
         <v>-266000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>688000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>154000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>774000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>625000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1237,9 +1273,12 @@
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1279,51 +1318,57 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>155000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1190000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>749000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-266000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>688000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>129000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>771000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>623000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>215000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-233000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1272000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1296000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>776700</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1355,17 +1400,20 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>13000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>19000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6200</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1405,93 +1453,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>155000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1190000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>749000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-266000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>688000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>129000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>771000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>623000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>215000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-233000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1259000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1277000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>770500</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1295000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>649000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-362000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>628000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>93000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>733000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>595000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>187000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-256000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1245000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1267000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>770500</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1531,9 +1588,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1573,9 +1633,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1615,9 +1678,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1657,17 +1723,20 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -1699,51 +1768,57 @@
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1295000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>649000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-362000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>628000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>93000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>733000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>595000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>187000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-256000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1245000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1267000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>770500</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1783,98 +1858,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1295000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>649000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-362000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>628000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>93000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>733000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>595000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>187000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-256000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1245000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1267000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>770500</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1891,8 +1975,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1909,50 +1994,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>518000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1018000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>998000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1017000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>831000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>921000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1046000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1208000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1110000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1720000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2143000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2430000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1367000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1992,51 +2081,57 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
         <v>120000</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
       <c r="F43" s="3">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
         <v>210000</v>
       </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
       <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
         <v>489000</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
       <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
         <v>7737000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1713000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5457000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2533000</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
       <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
         <v>461800</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2076,9 +2171,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2118,9 +2216,12 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2160,51 +2261,57 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>68026000</v>
+      </c>
+      <c r="E47" s="3">
         <v>47904000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>65367000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>78162000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>110720000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>106146000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>68070000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>46681000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>52531000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>59243000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>70000000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>97063000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>54784000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2244,9 +2351,12 @@
       <c r="O48" s="3">
         <v>0</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2266,14 +2376,14 @@
         <v>526000</v>
       </c>
       <c r="I49" s="3">
+        <v>526000</v>
+      </c>
+      <c r="J49" s="3">
         <v>551000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>554000</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2286,9 +2396,12 @@
       <c r="O49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2328,9 +2441,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2370,51 +2486,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1253000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1316000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>527000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1307000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>451000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>599000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>317000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>74000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1281000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>713000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>101000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>399000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>336000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2454,51 +2576,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>71596000</v>
+      </c>
+      <c r="E54" s="3">
         <v>51748000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>68149000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>81817000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>113082000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>109241000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>70376000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>56880000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>57021000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>67766000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>76255000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>100453000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>57972000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2515,8 +2643,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2533,134 +2662,144 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="3">
         <v>400000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>219000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>424000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>518000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>299000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>211000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>61000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>100000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>492000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>132000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>40000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>50426000</v>
+      </c>
+      <c r="E58" s="3">
         <v>36262000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>47381000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>52366000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>86857000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>75717000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>50296000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>40895000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>45507000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>50296000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>63533000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>75415000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>47735000</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>325000</v>
+      </c>
+      <c r="E59" s="3">
         <v>402000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>168000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6247000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2658000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1310000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>175000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>66000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>256000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>928000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>353000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>983000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2233000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2700,51 +2839,57 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E61" s="3">
         <v>95000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>126000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>177000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2553000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>275000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>357000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>460000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>595000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>761000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>910000</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2784,9 +2929,12 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2826,9 +2974,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2868,9 +3019,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2910,51 +3064,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>63339000</v>
+      </c>
+      <c r="E66" s="3">
         <v>43878000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>57858000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>70738000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>102041000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>99335000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>61622000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>49524000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>49050000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>58338000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>67558000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>89557000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>51760000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2971,8 +3131,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3012,9 +3173,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3054,9 +3218,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3064,22 +3231,22 @@
         <v>1634000</v>
       </c>
       <c r="E70" s="3">
-        <v>1489000</v>
+        <v>1634000</v>
       </c>
       <c r="F70" s="3">
         <v>1489000</v>
       </c>
       <c r="G70" s="3">
+        <v>1489000</v>
+      </c>
+      <c r="H70" s="3">
         <v>932000</v>
-      </c>
-      <c r="H70" s="3">
-        <v>484000</v>
       </c>
       <c r="I70" s="3">
         <v>484000</v>
       </c>
       <c r="J70" s="3">
-        <v>336000</v>
+        <v>484000</v>
       </c>
       <c r="K70" s="3">
         <v>336000</v>
@@ -3088,17 +3255,20 @@
         <v>336000</v>
       </c>
       <c r="M70" s="3">
-        <v>167000</v>
+        <v>336000</v>
       </c>
       <c r="N70" s="3">
         <v>167000</v>
       </c>
       <c r="O70" s="3">
-        <v>0</v>
-      </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+        <v>167000</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3138,51 +3308,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-8148000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-7284000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-5214000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-5106000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3886000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3433000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2562000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2518000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2350000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1674000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-497000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-289000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-38000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3222,9 +3398,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3264,9 +3443,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3306,51 +3488,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6623000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6236000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8802000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9590000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10109000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9422000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8270000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7020000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7635000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9092000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8530000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10729000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6212000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3390,98 +3578,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1295000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>649000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-362000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>628000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>93000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>733000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>595000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>187000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-256000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1245000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1267000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>770500</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3498,8 +3695,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3509,24 +3707,24 @@
       <c r="E83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G83" s="3">
         <v>0</v>
       </c>
       <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
         <v>25000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2000</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
@@ -3539,9 +3737,12 @@
       <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3581,9 +3782,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3623,9 +3827,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3665,9 +3872,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3707,9 +3917,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3749,51 +3962,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-118000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1013000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1540000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1747000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1180000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1113000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1260000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1352000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1428000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1622000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2501000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2321000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1070000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3810,8 +4029,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3851,9 +4071,12 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3893,9 +4116,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3935,51 +4161,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14672000</v>
+      </c>
+      <c r="E94" s="3">
         <v>11188000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>3836000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>36525000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-14218000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-27936000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11061000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>3201000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>4093000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>12349000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>8875000</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P94" s="3">
         <v>-39572000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3996,50 +4228,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-1005000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-869000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-860000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-970000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-1139000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-974000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-1590000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-799000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-902000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1094000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1659000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1415000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-664000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4079,9 +4315,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4121,9 +4360,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4163,51 +4405,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>14227000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11392000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6175000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-37230000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>12800000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>26980000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>9882000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5662000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6131000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-14394000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-11663000</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P100" s="3">
         <v>39696000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4241,55 +4489,61 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-563000</v>
+      </c>
+      <c r="E102" s="3">
         <v>809000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-799000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1042000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-238000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>157000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>81000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1109000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-610000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-423000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-287000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1063000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1194000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/AGNC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AGNC_YR_FIN.xlsx
@@ -2714,25 +2714,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>50426000</v>
+        <v>61320000</v>
       </c>
       <c r="E58" s="3">
-        <v>36262000</v>
+        <v>42796000</v>
       </c>
       <c r="F58" s="3">
-        <v>47381000</v>
+        <v>57078000</v>
       </c>
       <c r="G58" s="3">
-        <v>52366000</v>
+        <v>64093000</v>
       </c>
       <c r="H58" s="3">
-        <v>86857000</v>
+        <v>96400000</v>
       </c>
       <c r="I58" s="3">
-        <v>75717000</v>
+        <v>97148000</v>
       </c>
       <c r="J58" s="3">
-        <v>50296000</v>
+        <v>60763000</v>
       </c>
       <c r="K58" s="3">
         <v>40895000</v>

--- a/AAII_Financials/Yearly/AGNC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AGNC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
   <si>
     <t>AGNC</t>
   </si>
@@ -734,25 +734,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2538000</v>
+        <v>251000</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="3">
-        <v>912000</v>
-      </c>
-      <c r="G8" s="3">
-        <v>501000</v>
+        <v>837000</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H8" s="3">
-        <v>2920000</v>
+        <v>771000</v>
       </c>
       <c r="I8" s="3">
-        <v>1360000</v>
+        <v>229000</v>
       </c>
       <c r="J8" s="3">
-        <v>1365000</v>
+        <v>844000</v>
       </c>
       <c r="K8" s="3">
         <v>1122000</v>
@@ -778,26 +778,26 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>2287000</v>
-      </c>
-      <c r="E9" s="3">
-        <v>625000</v>
-      </c>
-      <c r="F9" s="3">
-        <v>75000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>674000</v>
-      </c>
-      <c r="H9" s="3">
-        <v>2149000</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1173000</v>
-      </c>
-      <c r="J9" s="3">
-        <v>524000</v>
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K9" s="3">
         <v>446000</v>
@@ -826,8 +826,8 @@
       <c r="D10" s="3">
         <v>251000</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>8</v>
+      <c r="E10" s="3">
+        <v>-1116000</v>
       </c>
       <c r="F10" s="3">
         <v>837000</v>
@@ -839,10 +839,10 @@
         <v>771000</v>
       </c>
       <c r="I10" s="3">
-        <v>187000</v>
+        <v>229000</v>
       </c>
       <c r="J10" s="3">
-        <v>841000</v>
+        <v>844000</v>
       </c>
       <c r="K10" s="3">
         <v>676000</v>
@@ -993,7 +993,7 @@
         <v>8</v>
       </c>
       <c r="I14" s="3">
-        <v>-42000</v>
+        <v>27000</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
@@ -1035,13 +1035,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1084,25 +1084,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2383000</v>
+        <v>96000</v>
       </c>
       <c r="E17" s="3">
-        <v>699000</v>
+        <v>74000</v>
       </c>
       <c r="F17" s="3">
-        <v>163000</v>
+        <v>88000</v>
       </c>
       <c r="G17" s="3">
-        <v>767000</v>
+        <v>93000</v>
       </c>
       <c r="H17" s="3">
-        <v>2232000</v>
+        <v>83000</v>
       </c>
       <c r="I17" s="3">
-        <v>1231000</v>
+        <v>73000</v>
       </c>
       <c r="J17" s="3">
-        <v>594000</v>
+        <v>73000</v>
       </c>
       <c r="K17" s="3">
         <v>499000</v>
@@ -1131,8 +1131,8 @@
       <c r="D18" s="3">
         <v>155000</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>8</v>
+      <c r="E18" s="3">
+        <v>-1190000</v>
       </c>
       <c r="F18" s="3">
         <v>749000</v>
@@ -1144,7 +1144,7 @@
         <v>688000</v>
       </c>
       <c r="I18" s="3">
-        <v>129000</v>
+        <v>156000</v>
       </c>
       <c r="J18" s="3">
         <v>771000</v>
@@ -1192,26 +1192,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1237,23 +1237,23 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>155000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1190000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>749000</v>
       </c>
       <c r="G21" s="3">
         <v>-266000</v>
       </c>
       <c r="H21" s="3">
-        <v>688000</v>
+        <v>713000</v>
       </c>
       <c r="I21" s="3">
-        <v>154000</v>
+        <v>181000</v>
       </c>
       <c r="J21" s="3">
         <v>774000</v>
@@ -1282,26 +1282,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1372,26 +1372,26 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1732,26 +1732,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1778,25 +1778,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>32000</v>
+        <v>155000</v>
       </c>
       <c r="E33" s="3">
-        <v>-1295000</v>
+        <v>-1190000</v>
       </c>
       <c r="F33" s="3">
-        <v>649000</v>
+        <v>749000</v>
       </c>
       <c r="G33" s="3">
-        <v>-362000</v>
+        <v>-266000</v>
       </c>
       <c r="H33" s="3">
-        <v>628000</v>
+        <v>688000</v>
       </c>
       <c r="I33" s="3">
-        <v>93000</v>
+        <v>129000</v>
       </c>
       <c r="J33" s="3">
-        <v>733000</v>
+        <v>771000</v>
       </c>
       <c r="K33" s="3">
         <v>595000</v>
@@ -1868,25 +1868,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>32000</v>
+        <v>155000</v>
       </c>
       <c r="E35" s="3">
-        <v>-1295000</v>
+        <v>-1190000</v>
       </c>
       <c r="F35" s="3">
-        <v>649000</v>
+        <v>749000</v>
       </c>
       <c r="G35" s="3">
-        <v>-362000</v>
+        <v>-266000</v>
       </c>
       <c r="H35" s="3">
-        <v>628000</v>
+        <v>688000</v>
       </c>
       <c r="I35" s="3">
-        <v>93000</v>
+        <v>129000</v>
       </c>
       <c r="J35" s="3">
-        <v>733000</v>
+        <v>771000</v>
       </c>
       <c r="K35" s="3">
         <v>595000</v>
@@ -2046,25 +2046,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>11803000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>7239000</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>10792000</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>12139000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>10371000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>22086000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>11166000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2090,26 +2090,26 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E43" s="3">
         <v>120000</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
+      <c r="F43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G43" s="3">
         <v>210000</v>
       </c>
-      <c r="H43" s="3">
-        <v>0</v>
+      <c r="H43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I43" s="3">
         <v>489000</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="J43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K43" s="3">
         <v>7737000</v>
@@ -2135,26 +2135,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2180,26 +2180,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2226,25 +2226,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>13574000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>9693000</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>12317000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>14673000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>11653000</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>24095000</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>12529000</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2271,25 +2271,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>68026000</v>
+        <v>5772000</v>
       </c>
       <c r="E47" s="3">
-        <v>47904000</v>
+        <v>4030000</v>
       </c>
       <c r="F47" s="3">
-        <v>65367000</v>
+        <v>6002000</v>
       </c>
       <c r="G47" s="3">
-        <v>78162000</v>
+        <v>11508000</v>
       </c>
       <c r="H47" s="3">
-        <v>110720000</v>
+        <v>7154000</v>
       </c>
       <c r="I47" s="3">
-        <v>106146000</v>
+        <v>5092000</v>
       </c>
       <c r="J47" s="3">
-        <v>68070000</v>
+        <v>3392000</v>
       </c>
       <c r="K47" s="3">
         <v>46681000</v>
@@ -2315,26 +2315,26 @@
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -2496,25 +2496,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1253000</v>
+        <v>51724000</v>
       </c>
       <c r="E52" s="3">
-        <v>1316000</v>
+        <v>37499000</v>
       </c>
       <c r="F52" s="3">
-        <v>527000</v>
+        <v>49304000</v>
       </c>
       <c r="G52" s="3">
-        <v>1307000</v>
+        <v>55110000</v>
       </c>
       <c r="H52" s="3">
-        <v>451000</v>
+        <v>93749000</v>
       </c>
       <c r="I52" s="3">
-        <v>599000</v>
+        <v>79528000</v>
       </c>
       <c r="J52" s="3">
-        <v>317000</v>
+        <v>53904000</v>
       </c>
       <c r="K52" s="3">
         <v>74000</v>
@@ -2668,26 +2668,26 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>8</v>
+      <c r="D57" s="3">
+        <v>210000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>302000</v>
       </c>
       <c r="F57" s="3">
-        <v>400000</v>
+        <v>80000</v>
       </c>
       <c r="G57" s="3">
-        <v>219000</v>
+        <v>6376000</v>
       </c>
       <c r="H57" s="3">
-        <v>424000</v>
+        <v>2978000</v>
       </c>
       <c r="I57" s="3">
-        <v>518000</v>
+        <v>1722000</v>
       </c>
       <c r="J57" s="3">
-        <v>299000</v>
+        <v>312000</v>
       </c>
       <c r="K57" s="3">
         <v>211000</v>
@@ -2714,25 +2714,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>61320000</v>
+        <v>50788000</v>
       </c>
       <c r="E58" s="3">
-        <v>42796000</v>
+        <v>36361000</v>
       </c>
       <c r="F58" s="3">
-        <v>57078000</v>
+        <v>47467000</v>
       </c>
       <c r="G58" s="3">
-        <v>64093000</v>
+        <v>52368000</v>
       </c>
       <c r="H58" s="3">
-        <v>96400000</v>
+        <v>86863000</v>
       </c>
       <c r="I58" s="3">
-        <v>97148000</v>
+        <v>72976000</v>
       </c>
       <c r="J58" s="3">
-        <v>60763000</v>
+        <v>45799000</v>
       </c>
       <c r="K58" s="3">
         <v>40895000</v>
@@ -2759,25 +2759,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>325000</v>
+        <v>11009000</v>
       </c>
       <c r="E59" s="3">
-        <v>402000</v>
+        <v>6634000</v>
       </c>
       <c r="F59" s="3">
-        <v>168000</v>
+        <v>9785000</v>
       </c>
       <c r="G59" s="3">
-        <v>6247000</v>
+        <v>11817000</v>
       </c>
       <c r="H59" s="3">
-        <v>2658000</v>
+        <v>9647000</v>
       </c>
       <c r="I59" s="3">
-        <v>1310000</v>
+        <v>21537000</v>
       </c>
       <c r="J59" s="3">
-        <v>175000</v>
+        <v>10629000</v>
       </c>
       <c r="K59" s="3">
         <v>66000</v>
@@ -2804,25 +2804,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>62007000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>43297000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>57332000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>70561000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>99488000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>96235000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>56740000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2864,10 +2864,10 @@
         <v>2553000</v>
       </c>
       <c r="I61" s="3">
-        <v>275000</v>
+        <v>3100000</v>
       </c>
       <c r="J61" s="3">
-        <v>357000</v>
+        <v>4882000</v>
       </c>
       <c r="K61" s="3">
         <v>460000</v>
@@ -2894,25 +2894,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>1252000</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>486000</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+        <v>400000</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3638,25 +3638,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>32000</v>
+        <v>155000</v>
       </c>
       <c r="E81" s="3">
-        <v>-1295000</v>
+        <v>-1190000</v>
       </c>
       <c r="F81" s="3">
-        <v>649000</v>
+        <v>749000</v>
       </c>
       <c r="G81" s="3">
-        <v>-362000</v>
+        <v>-266000</v>
       </c>
       <c r="H81" s="3">
-        <v>628000</v>
+        <v>688000</v>
       </c>
       <c r="I81" s="3">
-        <v>93000</v>
+        <v>129000</v>
       </c>
       <c r="J81" s="3">
-        <v>733000</v>
+        <v>771000</v>
       </c>
       <c r="K81" s="3">
         <v>595000</v>
@@ -3710,17 +3710,17 @@
       <c r="F83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>25000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>3000</v>
+      <c r="G83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K83" s="3">
         <v>2000</v>
@@ -4035,26 +4035,26 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4235,25 +4235,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1005000</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-869000</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-860000</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-970000</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-1139000</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-974000</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>-1590000</v>
+        <v>0</v>
       </c>
       <c r="K96" s="3">
         <v>-799000</v>
@@ -4459,26 +4459,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/AGNC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AGNC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="92">
   <si>
     <t>AGNC</t>
   </si>
@@ -656,125 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>973000</v>
+      </c>
+      <c r="E8" s="3">
         <v>251000</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3">
         <v>837000</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3">
         <v>771000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>229000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>844000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1122000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>684000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>280000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1976000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1952000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1135200</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -799,72 +805,78 @@
       <c r="J9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="3">
-        <v>446000</v>
+      <c r="K9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L9" s="3">
         <v>446000</v>
       </c>
       <c r="M9" s="3">
+        <v>446000</v>
+      </c>
+      <c r="N9" s="3">
         <v>491000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>672000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>625000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>339400</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>973000</v>
+      </c>
+      <c r="E10" s="3">
         <v>251000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-1116000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>837000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-173000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>771000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>229000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>844000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>676000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>238000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-211000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1304000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1327000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>795800</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -882,8 +894,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -926,9 +939,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -971,9 +987,12 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -992,12 +1011,12 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>27000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1007,8 +1026,8 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1016,9 +1035,12 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1035,17 +1057,17 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
         <v>25000</v>
       </c>
       <c r="J15" s="3">
+        <v>25000</v>
+      </c>
+      <c r="K15" s="3">
         <v>3000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1061,9 +1083,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1078,98 +1103,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>110000</v>
+      </c>
+      <c r="E17" s="3">
         <v>96000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>74000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>88000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>93000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>83000</v>
-      </c>
-      <c r="I17" s="3">
-        <v>73000</v>
       </c>
       <c r="J17" s="3">
         <v>73000</v>
       </c>
       <c r="K17" s="3">
+        <v>73000</v>
+      </c>
+      <c r="L17" s="3">
         <v>499000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>469000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>513000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>704000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>656000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>358500</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>863000</v>
+      </c>
+      <c r="E18" s="3">
         <v>155000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1190000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>749000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-266000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>688000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>156000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>771000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>623000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>215000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-233000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1272000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1296000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>776700</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1187,8 +1219,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1213,8 +1246,8 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1231,39 +1264,42 @@
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>863000</v>
+      </c>
+      <c r="E21" s="3">
         <v>155000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1190000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>749000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-266000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>713000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>181000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>774000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>625000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1276,9 +1312,12 @@
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1303,8 +1342,8 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1321,54 +1360,60 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>863000</v>
+      </c>
+      <c r="E23" s="3">
         <v>155000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1190000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>749000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-266000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>688000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>129000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>771000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>623000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>215000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-233000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1272000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1296000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>776700</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1393,8 +1438,8 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1403,17 +1448,20 @@
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>13000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>19000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6200</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1456,99 +1504,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>863000</v>
+      </c>
+      <c r="E26" s="3">
         <v>155000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1190000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>749000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-266000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>688000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>129000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>771000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>623000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>215000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-233000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1259000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1277000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>770500</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>731000</v>
+      </c>
+      <c r="E27" s="3">
         <v>32000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1295000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>649000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-362000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>628000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>93000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>733000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>595000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>187000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-256000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1245000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1267000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>770500</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1591,9 +1648,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1636,9 +1696,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1681,9 +1744,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1726,9 +1792,12 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1753,8 +1822,8 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -1771,54 +1840,60 @@
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>863000</v>
+      </c>
+      <c r="E33" s="3">
         <v>155000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1190000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>749000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-266000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>688000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>129000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>771000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>595000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>187000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-256000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1245000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1267000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>770500</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1861,104 +1936,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>863000</v>
+      </c>
+      <c r="E35" s="3">
         <v>155000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1190000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>749000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-266000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>688000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>129000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>771000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>595000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>187000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-256000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1245000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1267000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>770500</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1976,8 +2060,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1995,80 +2080,84 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>505000</v>
+      </c>
+      <c r="E41" s="3">
         <v>518000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1018000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>998000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1017000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>831000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>921000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1046000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1208000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1110000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1720000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2143000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2430000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1367000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>17342000</v>
+      </c>
+      <c r="E42" s="3">
         <v>11803000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>7239000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10792000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12139000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>10371000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>22086000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>11166000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2084,54 +2173,60 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="3">
         <v>120000</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H43" s="3">
         <v>210000</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3">
         <v>489000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L43" s="3">
         <v>7737000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1713000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5457000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2533000</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
         <v>461800</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2156,8 +2251,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2174,9 +2269,12 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2201,8 +2299,8 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -2219,36 +2317,39 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19113000</v>
+      </c>
+      <c r="E46" s="3">
         <v>13574000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9693000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12317000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14673000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11653000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>24095000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12529000</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2264,54 +2365,60 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>5772000</v>
+        <v>5577000</v>
       </c>
       <c r="E47" s="3">
+        <v>4242000</v>
+      </c>
+      <c r="F47" s="3">
         <v>4030000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6002000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>11508000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7154000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5092000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3392000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>46681000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>52531000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>59243000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>70000000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>97063000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>54784000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2336,8 +2443,8 @@
       <c r="J48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -2354,9 +2461,12 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2379,14 +2489,14 @@
         <v>526000</v>
       </c>
       <c r="J49" s="3">
+        <v>526000</v>
+      </c>
+      <c r="K49" s="3">
         <v>551000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>554000</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2399,9 +2509,12 @@
       <c r="P49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2444,9 +2557,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2489,54 +2605,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>51724000</v>
+        <v>62799000</v>
       </c>
       <c r="E52" s="3">
+        <v>53254000</v>
+      </c>
+      <c r="F52" s="3">
         <v>37499000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>49304000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>55110000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>93749000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>79528000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>53904000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>74000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1281000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>713000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>101000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>399000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>336000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2579,54 +2701,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>88015000</v>
+      </c>
+      <c r="E54" s="3">
         <v>71596000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>51748000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>68149000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>81817000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>113082000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>109241000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>70376000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>56880000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>57021000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>67766000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>76255000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>100453000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>57972000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2644,8 +2772,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2663,170 +2792,180 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E57" s="3">
         <v>210000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>302000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>80000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6376000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2978000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1722000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>312000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>211000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>61000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>100000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>492000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>132000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>40000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>60892000</v>
+      </c>
+      <c r="E58" s="3">
         <v>50788000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>36361000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>47467000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>52368000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>86863000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>72976000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>45799000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>40895000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>45507000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>50296000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>63533000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>75415000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>47735000</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16819000</v>
+      </c>
+      <c r="E59" s="3">
         <v>11009000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6634000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9785000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11817000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9647000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21537000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10629000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>66000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>256000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>928000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>353000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>983000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2233000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>77785000</v>
+      </c>
+      <c r="E60" s="3">
         <v>62007000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>43297000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>57332000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>70561000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>99488000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>96235000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>56740000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2842,69 +2981,75 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E61" s="3">
         <v>80000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>95000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>126000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>177000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2553000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3100000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4882000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>460000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>595000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>761000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>910000</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>404000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1252000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>486000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>400000</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>8</v>
       </c>
@@ -2914,8 +3059,8 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -2932,9 +3077,12 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2977,9 +3125,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3022,9 +3173,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3067,54 +3221,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>78253000</v>
+      </c>
+      <c r="E66" s="3">
         <v>63339000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>43878000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>57858000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>70738000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>102041000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>99335000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>61622000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>49524000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>49050000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>58338000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>67558000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>89557000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>51760000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3132,8 +3292,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3176,9 +3337,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3221,9 +3385,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3234,22 +3401,22 @@
         <v>1634000</v>
       </c>
       <c r="F70" s="3">
-        <v>1489000</v>
+        <v>1634000</v>
       </c>
       <c r="G70" s="3">
         <v>1489000</v>
       </c>
       <c r="H70" s="3">
+        <v>1489000</v>
+      </c>
+      <c r="I70" s="3">
         <v>932000</v>
-      </c>
-      <c r="I70" s="3">
-        <v>484000</v>
       </c>
       <c r="J70" s="3">
         <v>484000</v>
       </c>
       <c r="K70" s="3">
-        <v>336000</v>
+        <v>484000</v>
       </c>
       <c r="L70" s="3">
         <v>336000</v>
@@ -3258,17 +3425,20 @@
         <v>336000</v>
       </c>
       <c r="N70" s="3">
-        <v>167000</v>
+        <v>336000</v>
       </c>
       <c r="O70" s="3">
         <v>167000</v>
       </c>
       <c r="P70" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+        <v>167000</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3311,54 +3481,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-8554000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-8148000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-7284000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-5214000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-5106000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3886000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3433000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2562000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2518000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2350000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1674000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-497000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-289000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-38000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3401,9 +3577,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3446,9 +3625,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3491,54 +3673,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8128000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6623000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6236000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8802000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9590000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10109000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9422000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8270000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7020000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7635000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9092000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8530000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10729000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6212000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3581,104 +3769,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>863000</v>
+      </c>
+      <c r="E81" s="3">
         <v>155000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1190000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>749000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-266000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>688000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>129000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>771000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>595000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>187000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-256000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1245000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1267000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>770500</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3696,8 +3893,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3722,12 +3920,12 @@
       <c r="J83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L83" s="3">
         <v>2000</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>8</v>
       </c>
@@ -3740,9 +3938,12 @@
       <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3785,9 +3986,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3830,9 +4034,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3875,9 +4082,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3920,9 +4130,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3965,54 +4178,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>86000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-118000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1013000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1540000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1747000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1180000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1113000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1260000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1352000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1428000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1622000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2501000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2321000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1070000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4030,8 +4249,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4056,8 +4276,8 @@
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -4074,9 +4294,12 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4119,9 +4342,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4164,54 +4390,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-11169000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-14672000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>11188000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>3836000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>36525000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14218000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-27936000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11061000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3201000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>4093000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>12349000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>8875000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-39572000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4229,8 +4461,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4256,26 +4489,29 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-799000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-902000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1094000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1659000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1415000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-664000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4318,9 +4554,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4363,9 +4602,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4408,54 +4650,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>11083000</v>
+      </c>
+      <c r="E100" s="3">
         <v>14227000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11392000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6175000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-37230000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>12800000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>26980000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>9882000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5662000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6131000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-14394000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-11663000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q100" s="3">
         <v>39696000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4480,8 +4728,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4492,58 +4740,64 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-563000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>809000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-799000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1042000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-238000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>157000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>81000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1109000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-610000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-423000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-287000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1063000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1194000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/AGNC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AGNC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
   <si>
     <t>AGNC</t>
   </si>
@@ -656,131 +656,138 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1797000</v>
+      </c>
+      <c r="E8" s="3">
         <v>973000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>251000</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3">
         <v>837000</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3">
         <v>771000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>229000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>844000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1122000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>684000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>280000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1976000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1952000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1135200</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -808,75 +815,81 @@
       <c r="K9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="3">
-        <v>446000</v>
+      <c r="L9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M9" s="3">
         <v>446000</v>
       </c>
       <c r="N9" s="3">
+        <v>446000</v>
+      </c>
+      <c r="O9" s="3">
         <v>491000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>672000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>625000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>339400</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1797000</v>
+      </c>
+      <c r="E10" s="3">
         <v>973000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>251000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-1116000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>837000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-173000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>771000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>229000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>844000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>676000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>238000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-211000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1304000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1327000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>795800</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -895,8 +908,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -942,9 +956,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -990,9 +1007,12 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1014,12 +1034,12 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>27000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1029,8 +1049,8 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1038,9 +1058,12 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1060,17 +1083,17 @@
         <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>25000</v>
       </c>
       <c r="K15" s="3">
+        <v>25000</v>
+      </c>
+      <c r="L15" s="3">
         <v>3000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1086,9 +1109,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1104,104 +1130,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E17" s="3">
         <v>110000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>96000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>74000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>88000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>93000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>83000</v>
-      </c>
-      <c r="J17" s="3">
-        <v>73000</v>
       </c>
       <c r="K17" s="3">
         <v>73000</v>
       </c>
       <c r="L17" s="3">
+        <v>73000</v>
+      </c>
+      <c r="M17" s="3">
         <v>499000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>469000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>513000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>704000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>656000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>358500</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1670000</v>
+      </c>
+      <c r="E18" s="3">
         <v>863000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>155000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1190000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>749000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-266000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>688000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>156000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>771000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>623000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>215000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-233000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1272000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1296000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>776700</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1220,8 +1253,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1249,8 +1283,8 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1267,42 +1301,45 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1670000</v>
+      </c>
+      <c r="E21" s="3">
         <v>863000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>155000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1190000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>749000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-266000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>713000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>181000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>774000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>625000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1315,9 +1352,12 @@
       <c r="Q21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1345,8 +1385,8 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1363,57 +1403,63 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1670000</v>
+      </c>
+      <c r="E23" s="3">
         <v>863000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>155000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1190000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>749000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-266000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>688000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>129000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>771000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>623000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>215000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-233000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1272000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1296000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>776700</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1441,8 +1487,8 @@
       <c r="K24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1451,17 +1497,20 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>13000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>19000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6200</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1507,105 +1556,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1670000</v>
+      </c>
+      <c r="E26" s="3">
         <v>863000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>155000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1190000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>749000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-266000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>688000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>129000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>771000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>623000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>215000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-233000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1259000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1277000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>770500</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1509000</v>
+      </c>
+      <c r="E27" s="3">
         <v>731000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>32000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1295000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>649000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-362000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>628000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>93000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>733000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>595000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>187000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-256000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1245000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1267000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>770500</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1651,9 +1709,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1699,9 +1760,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1747,9 +1811,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1795,9 +1862,12 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1825,8 +1895,8 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -1843,57 +1913,63 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1670000</v>
+      </c>
+      <c r="E33" s="3">
         <v>863000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>155000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1190000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>749000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-266000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>688000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>129000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>771000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>595000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>187000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-256000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1245000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1267000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>770500</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1939,110 +2015,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1670000</v>
+      </c>
+      <c r="E35" s="3">
         <v>863000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>155000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1190000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>749000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-266000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>688000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>129000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>771000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>595000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>187000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-256000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1245000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1267000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>770500</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2061,8 +2146,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2081,86 +2167,90 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>450000</v>
+      </c>
+      <c r="E41" s="3">
         <v>505000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>518000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1018000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>998000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1017000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>831000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>921000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1046000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1208000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1110000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1720000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2143000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2430000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1367000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>16784000</v>
+      </c>
+      <c r="E42" s="3">
         <v>17342000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>11803000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7239000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>10792000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12139000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>10371000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>22086000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11166000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2176,57 +2266,63 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>8</v>
+      <c r="D43" s="3">
+        <v>152000</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="3">
         <v>120000</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="3">
         <v>210000</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" s="3">
         <v>489000</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M43" s="3">
         <v>7737000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1713000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5457000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2533000</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
         <v>461800</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2254,8 +2350,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2272,9 +2368,12 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2302,8 +2401,8 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
+      <c r="L45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -2320,39 +2419,42 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18678000</v>
+      </c>
+      <c r="E46" s="3">
         <v>19113000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13574000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9693000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12317000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14673000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11653000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>24095000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12529000</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2368,57 +2470,63 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7405000</v>
+      </c>
+      <c r="E47" s="3">
         <v>5577000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4242000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4030000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6002000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>11508000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7154000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5092000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3392000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>46681000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>52531000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>59243000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>70000000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>97063000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>54784000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2446,8 +2554,8 @@
       <c r="K48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -2464,9 +2572,12 @@
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2492,14 +2603,14 @@
         <v>526000</v>
       </c>
       <c r="K49" s="3">
+        <v>526000</v>
+      </c>
+      <c r="L49" s="3">
         <v>551000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>554000</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2512,9 +2623,12 @@
       <c r="Q49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2560,9 +2674,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2608,57 +2725,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>88468000</v>
+      </c>
+      <c r="E52" s="3">
         <v>62799000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>53254000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>37499000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>49304000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>55110000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>93749000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>79528000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>53904000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>74000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1281000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>713000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>101000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>399000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>336000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2704,57 +2827,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>115077000</v>
+      </c>
+      <c r="E54" s="3">
         <v>88015000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>71596000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>51748000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>68149000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>81817000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>113082000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>109241000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>70376000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>56880000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>57021000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>67766000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>76255000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>100453000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>57972000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2773,8 +2902,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2793,182 +2923,192 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>193000</v>
+      </c>
+      <c r="E57" s="3">
         <v>74000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>210000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>302000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>80000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6376000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2978000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1722000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>312000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>211000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>61000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>100000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>492000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>132000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>40000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>85292000</v>
+      </c>
+      <c r="E58" s="3">
         <v>60892000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>50788000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>36361000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>47467000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>52368000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>86863000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>72976000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>45799000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>40895000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>45507000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>50296000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>63533000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>75415000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>47735000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16634000</v>
+      </c>
+      <c r="E59" s="3">
         <v>16819000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11009000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6634000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9785000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11817000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9647000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>21537000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10629000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>66000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>256000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>928000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>353000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>983000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2233000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>102119000</v>
+      </c>
+      <c r="E60" s="3">
         <v>77785000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>62007000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>43297000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>57332000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>70561000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>99488000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>96235000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>56740000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2984,75 +3124,81 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E61" s="3">
         <v>64000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>80000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>95000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>126000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>177000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2553000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3100000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4882000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>460000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>595000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>761000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>910000</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>509000</v>
+      </c>
+      <c r="E62" s="3">
         <v>404000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1252000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>486000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>400000</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>8</v>
       </c>
@@ -3062,8 +3208,8 @@
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -3080,9 +3226,12 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3128,9 +3277,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3176,9 +3328,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3224,57 +3379,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>102684000</v>
+      </c>
+      <c r="E66" s="3">
         <v>78253000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>63339000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>43878000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>57858000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>70738000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>102041000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>99335000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>61622000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>49524000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>49050000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>58338000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>67558000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>89557000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>51760000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3293,8 +3454,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3340,9 +3502,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3388,14 +3553,17 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>1634000</v>
+        <v>1968000</v>
       </c>
       <c r="E70" s="3">
         <v>1634000</v>
@@ -3404,22 +3572,22 @@
         <v>1634000</v>
       </c>
       <c r="G70" s="3">
-        <v>1489000</v>
+        <v>1634000</v>
       </c>
       <c r="H70" s="3">
         <v>1489000</v>
       </c>
       <c r="I70" s="3">
+        <v>1489000</v>
+      </c>
+      <c r="J70" s="3">
         <v>932000</v>
-      </c>
-      <c r="J70" s="3">
-        <v>484000</v>
       </c>
       <c r="K70" s="3">
         <v>484000</v>
       </c>
       <c r="L70" s="3">
-        <v>336000</v>
+        <v>484000</v>
       </c>
       <c r="M70" s="3">
         <v>336000</v>
@@ -3428,17 +3596,20 @@
         <v>336000</v>
       </c>
       <c r="O70" s="3">
-        <v>167000</v>
+        <v>336000</v>
       </c>
       <c r="P70" s="3">
         <v>167000</v>
       </c>
       <c r="Q70" s="3">
-        <v>0</v>
-      </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+        <v>167000</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3484,57 +3655,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-8524000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-8554000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-8148000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-7284000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-5214000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-5106000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3886000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3433000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2562000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2518000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2350000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1674000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-497000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-289000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-38000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3580,9 +3757,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3628,9 +3808,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3676,57 +3859,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10425000</v>
+      </c>
+      <c r="E76" s="3">
         <v>8128000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6623000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6236000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8802000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9590000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10109000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9422000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8270000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7020000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7635000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9092000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8530000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10729000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6212000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3772,110 +3961,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1670000</v>
+      </c>
+      <c r="E81" s="3">
         <v>863000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>155000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1190000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>749000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-266000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>688000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>129000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>771000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>595000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>187000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-256000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1245000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1267000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>770500</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3894,8 +4092,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3923,12 +4122,12 @@
       <c r="K83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M83" s="3">
         <v>2000</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
@@ -3941,9 +4140,12 @@
       <c r="Q83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3989,9 +4191,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4037,9 +4242,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4085,9 +4293,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4133,9 +4344,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4181,57 +4395,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>653000</v>
+      </c>
+      <c r="E89" s="3">
         <v>86000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-118000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1013000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1540000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1747000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1180000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1113000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1260000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1352000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1428000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1622000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2501000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2321000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1070000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4250,8 +4470,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4279,8 +4500,8 @@
       <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -4297,9 +4518,12 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4345,9 +4569,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4393,57 +4620,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-25864000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-11169000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-14672000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>11188000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3836000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>36525000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14218000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-27936000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11061000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>3201000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>4093000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>12349000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>8875000</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R94" s="3">
         <v>-39572000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4462,8 +4695,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4492,26 +4726,29 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-799000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-902000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1094000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1659000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1415000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-664000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4557,9 +4794,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4605,9 +4845,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4653,57 +4896,63 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>25182000</v>
+      </c>
+      <c r="E100" s="3">
         <v>11083000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>14227000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11392000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6175000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-37230000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>12800000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>26980000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>9882000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5662000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6131000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-14394000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-11663000</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R100" s="3">
         <v>39696000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4731,8 +4980,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4743,61 +4992,67 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-29000</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-563000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>809000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-799000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1042000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-238000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>157000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>81000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1109000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-610000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-423000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-287000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1063000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1194000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
